--- a/seguimiento/galapa-6v091tb7/cronograma-ejecutado.xlsx
+++ b/seguimiento/galapa-6v091tb7/cronograma-ejecutado.xlsx
@@ -1683,10 +1683,8 @@
           <t>P</t>
         </is>
       </c>
-      <c r="R20" s="21" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+      <c r="R20" s="21" t="n">
+        <v>0.6</v>
       </c>
       <c r="S20" s="21" t="inlineStr">
         <is>
@@ -1926,10 +1924,8 @@
       <c r="P24" s="21" t="n">
         <v>0.86</v>
       </c>
-      <c r="Q24" s="21" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+      <c r="Q24" s="21" t="n">
+        <v>0.14</v>
       </c>
       <c r="R24" s="21" t="inlineStr">
         <is>
@@ -2165,7 +2161,9 @@
       <c r="O28" s="21" t="n"/>
       <c r="P28" s="21" t="n"/>
       <c r="Q28" s="21" t="n"/>
-      <c r="R28" s="21" t="n"/>
+      <c r="R28" s="21" t="n">
+        <v>0.45</v>
+      </c>
       <c r="S28" s="21" t="n"/>
       <c r="T28" s="21" t="n"/>
       <c r="U28" s="21" t="n"/>
@@ -3411,10 +3409,8 @@
           <t>P</t>
         </is>
       </c>
-      <c r="Q51" s="21" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+      <c r="Q51" s="21" t="n">
+        <v>0.24</v>
       </c>
       <c r="R51" s="21" t="inlineStr">
         <is>
@@ -4857,7 +4853,9 @@
         </is>
       </c>
       <c r="Q78" s="21" t="n"/>
-      <c r="R78" s="21" t="n"/>
+      <c r="R78" s="21" t="n">
+        <v>0.63</v>
+      </c>
       <c r="S78" s="21" t="n"/>
       <c r="T78" s="21" t="n"/>
       <c r="U78" s="21" t="n"/>
@@ -5077,7 +5075,9 @@
         </is>
       </c>
       <c r="Q82" s="21" t="n"/>
-      <c r="R82" s="21" t="n"/>
+      <c r="R82" s="21" t="n">
+        <v>0.34</v>
+      </c>
       <c r="S82" s="21" t="n"/>
       <c r="T82" s="21" t="n"/>
       <c r="U82" s="21" t="n"/>

--- a/seguimiento/galapa-6v091tb7/cronograma-ejecutado.xlsx
+++ b/seguimiento/galapa-6v091tb7/cronograma-ejecutado.xlsx
@@ -695,7 +695,7 @@
     <row r="5">
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>SEMANA DEL (LUNES)</t>
+          <t>SEMANA DEL</t>
         </is>
       </c>
       <c r="E5" s="10" t="n">
@@ -2164,7 +2164,9 @@
       <c r="R28" s="21" t="n">
         <v>0.45</v>
       </c>
-      <c r="S28" s="21" t="n"/>
+      <c r="S28" s="21" t="n">
+        <v>0.26</v>
+      </c>
       <c r="T28" s="21" t="n"/>
       <c r="U28" s="21" t="n"/>
       <c r="V28" s="21" t="n"/>
@@ -4966,7 +4968,9 @@
       </c>
       <c r="Q80" s="21" t="n"/>
       <c r="R80" s="21" t="n"/>
-      <c r="S80" s="21" t="n"/>
+      <c r="S80" s="21" t="n">
+        <v>0.33</v>
+      </c>
       <c r="T80" s="21" t="n"/>
       <c r="U80" s="21" t="n"/>
       <c r="V80" s="21" t="n"/>
@@ -5021,7 +5025,9 @@
       </c>
       <c r="Q81" s="21" t="n"/>
       <c r="R81" s="21" t="n"/>
-      <c r="S81" s="21" t="n"/>
+      <c r="S81" s="21" t="n">
+        <v>0.47</v>
+      </c>
       <c r="T81" s="21" t="n"/>
       <c r="U81" s="21" t="n"/>
       <c r="V81" s="21" t="n"/>
@@ -5078,7 +5084,9 @@
       <c r="R82" s="21" t="n">
         <v>0.34</v>
       </c>
-      <c r="S82" s="21" t="n"/>
+      <c r="S82" s="21" t="n">
+        <v>0.33</v>
+      </c>
       <c r="T82" s="21" t="n"/>
       <c r="U82" s="21" t="n"/>
       <c r="V82" s="21" t="n"/>

--- a/seguimiento/galapa-6v091tb7/cronograma-ejecutado.xlsx
+++ b/seguimiento/galapa-6v091tb7/cronograma-ejecutado.xlsx
@@ -4858,7 +4858,9 @@
       <c r="R78" s="21" t="n">
         <v>0.63</v>
       </c>
-      <c r="S78" s="21" t="n"/>
+      <c r="S78" s="21" t="n">
+        <v>0.07999999999999996</v>
+      </c>
       <c r="T78" s="21" t="n"/>
       <c r="U78" s="21" t="n"/>
       <c r="V78" s="21" t="n"/>
@@ -4913,7 +4915,9 @@
       </c>
       <c r="Q79" s="21" t="n"/>
       <c r="R79" s="21" t="n"/>
-      <c r="S79" s="21" t="n"/>
+      <c r="S79" s="21" t="n">
+        <v>0.21</v>
+      </c>
       <c r="T79" s="21" t="n"/>
       <c r="U79" s="21" t="n"/>
       <c r="V79" s="21" t="n"/>
@@ -4969,7 +4973,7 @@
       <c r="Q80" s="21" t="n"/>
       <c r="R80" s="21" t="n"/>
       <c r="S80" s="21" t="n">
-        <v>0.33</v>
+        <v>0.61</v>
       </c>
       <c r="T80" s="21" t="n"/>
       <c r="U80" s="21" t="n"/>

--- a/seguimiento/galapa-6v091tb7/cronograma-ejecutado.xlsx
+++ b/seguimiento/galapa-6v091tb7/cronograma-ejecutado.xlsx
@@ -18,11 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="dd/mm"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="dd/mm"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -127,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,7 +149,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -190,10 +189,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -698,79 +704,79 @@
           <t>SEMANA DEL</t>
         </is>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="26" t="n">
         <v>46216</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F5" s="26" t="n">
         <v>46223</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="26" t="n">
         <v>46230</v>
       </c>
-      <c r="H5" s="10" t="n">
+      <c r="H5" s="26" t="n">
         <v>46237</v>
       </c>
-      <c r="I5" s="10" t="n">
+      <c r="I5" s="26" t="n">
         <v>46244</v>
       </c>
-      <c r="J5" s="10" t="n">
+      <c r="J5" s="26" t="n">
         <v>46251</v>
       </c>
-      <c r="K5" s="10" t="n">
+      <c r="K5" s="26" t="n">
         <v>46258</v>
       </c>
-      <c r="L5" s="10" t="n">
+      <c r="L5" s="26" t="n">
         <v>46265</v>
       </c>
-      <c r="M5" s="10" t="n">
+      <c r="M5" s="26" t="n">
         <v>46272</v>
       </c>
-      <c r="N5" s="10" t="n">
+      <c r="N5" s="26" t="n">
         <v>46279</v>
       </c>
-      <c r="O5" s="10" t="n">
+      <c r="O5" s="26" t="n">
         <v>46286</v>
       </c>
-      <c r="P5" s="10" t="n">
+      <c r="P5" s="26" t="n">
         <v>46293</v>
       </c>
-      <c r="Q5" s="10" t="n">
+      <c r="Q5" s="26" t="n">
         <v>46300</v>
       </c>
-      <c r="R5" s="10" t="n">
+      <c r="R5" s="26" t="n">
         <v>46307</v>
       </c>
-      <c r="S5" s="10" t="n">
+      <c r="S5" s="26" t="n">
         <v>46314</v>
       </c>
-      <c r="T5" s="10" t="n">
+      <c r="T5" s="26" t="n">
         <v>46321</v>
       </c>
-      <c r="U5" s="10" t="n">
+      <c r="U5" s="26" t="n">
         <v>46328</v>
       </c>
-      <c r="V5" s="10" t="n">
+      <c r="V5" s="26" t="n">
         <v>46335</v>
       </c>
-      <c r="W5" s="10" t="n">
+      <c r="W5" s="26" t="n">
         <v>46342</v>
       </c>
-      <c r="X5" s="10" t="n">
+      <c r="X5" s="26" t="n">
         <v>46349</v>
       </c>
-      <c r="Y5" s="10" t="n">
+      <c r="Y5" s="26" t="n">
         <v>46356</v>
       </c>
-      <c r="Z5" s="10" t="n">
+      <c r="Z5" s="26" t="n">
         <v>46363</v>
       </c>
-      <c r="AA5" s="10" t="n">
+      <c r="AA5" s="26" t="n">
         <v>46370</v>
       </c>
-      <c r="AB5" s="10" t="n">
+      <c r="AB5" s="26" t="n">
         <v>46377</v>
       </c>
-      <c r="AC5" s="10" t="n">
+      <c r="AC5" s="26" t="n">
         <v>46384</v>
       </c>
     </row>
@@ -1625,7 +1631,7 @@
         </is>
       </c>
       <c r="P19" s="21" t="n">
-        <v>0.613829787234042</v>
+        <v>0.61383</v>
       </c>
       <c r="Q19" s="21" t="inlineStr">
         <is>
@@ -1634,7 +1640,9 @@
       </c>
       <c r="R19" s="21" t="n"/>
       <c r="S19" s="21" t="n"/>
-      <c r="T19" s="21" t="n"/>
+      <c r="T19" s="21" t="n">
+        <v>0.06</v>
+      </c>
       <c r="U19" s="21" t="n"/>
       <c r="V19" s="21" t="n"/>
       <c r="W19" s="21" t="n"/>
@@ -2091,7 +2099,7 @@
       <c r="N27" s="21" t="n"/>
       <c r="O27" s="21" t="n"/>
       <c r="P27" s="21" t="n">
-        <v>0.510204081632653</v>
+        <v>0.510204</v>
       </c>
       <c r="Q27" s="21" t="n"/>
       <c r="R27" s="21" t="n"/>
@@ -2167,7 +2175,9 @@
       <c r="S28" s="21" t="n">
         <v>0.26</v>
       </c>
-      <c r="T28" s="21" t="n"/>
+      <c r="T28" s="21" t="n">
+        <v>0.28</v>
+      </c>
       <c r="U28" s="21" t="n"/>
       <c r="V28" s="21" t="n"/>
       <c r="W28" s="21" t="n"/>
@@ -2477,10 +2487,8 @@
           <t>P</t>
         </is>
       </c>
-      <c r="T34" s="21" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+      <c r="T34" s="21" t="n">
+        <v>0.04</v>
       </c>
       <c r="U34" s="21" t="inlineStr">
         <is>
@@ -4178,7 +4186,9 @@
       <c r="Q65" s="21" t="n"/>
       <c r="R65" s="21" t="n"/>
       <c r="S65" s="21" t="n"/>
-      <c r="T65" s="21" t="n"/>
+      <c r="T65" s="21" t="n">
+        <v>0.04</v>
+      </c>
       <c r="U65" s="21" t="inlineStr">
         <is>
           <t>P</t>
@@ -4233,7 +4243,9 @@
       <c r="Q66" s="21" t="n"/>
       <c r="R66" s="21" t="n"/>
       <c r="S66" s="21" t="n"/>
-      <c r="T66" s="21" t="n"/>
+      <c r="T66" s="21" t="n">
+        <v>0.23</v>
+      </c>
       <c r="U66" s="21" t="inlineStr">
         <is>
           <t>P</t>
@@ -4802,7 +4814,9 @@
       <c r="Q77" s="21" t="n"/>
       <c r="R77" s="21" t="n"/>
       <c r="S77" s="21" t="n"/>
-      <c r="T77" s="21" t="n"/>
+      <c r="T77" s="21" t="n">
+        <v>0.2</v>
+      </c>
       <c r="U77" s="21" t="n"/>
       <c r="V77" s="21" t="n"/>
       <c r="W77" s="21" t="n"/>
@@ -4859,9 +4873,11 @@
         <v>0.63</v>
       </c>
       <c r="S78" s="21" t="n">
-        <v>0.07999999999999996</v>
-      </c>
-      <c r="T78" s="21" t="n"/>
+        <v>0.08</v>
+      </c>
+      <c r="T78" s="21" t="n">
+        <v>0.29</v>
+      </c>
       <c r="U78" s="21" t="n"/>
       <c r="V78" s="21" t="n"/>
       <c r="W78" s="21" t="n"/>
@@ -4918,7 +4934,9 @@
       <c r="S79" s="21" t="n">
         <v>0.21</v>
       </c>
-      <c r="T79" s="21" t="n"/>
+      <c r="T79" s="21" t="n">
+        <v>0.32</v>
+      </c>
       <c r="U79" s="21" t="n"/>
       <c r="V79" s="21" t="n"/>
       <c r="W79" s="21" t="n"/>
@@ -4975,7 +4993,9 @@
       <c r="S80" s="21" t="n">
         <v>0.61</v>
       </c>
-      <c r="T80" s="21" t="n"/>
+      <c r="T80" s="21" t="n">
+        <v>0.32</v>
+      </c>
       <c r="U80" s="21" t="n"/>
       <c r="V80" s="21" t="n"/>
       <c r="W80" s="21" t="n"/>
@@ -5032,7 +5052,9 @@
       <c r="S81" s="21" t="n">
         <v>0.47</v>
       </c>
-      <c r="T81" s="21" t="n"/>
+      <c r="T81" s="21" t="n">
+        <v>0.06</v>
+      </c>
       <c r="U81" s="21" t="n"/>
       <c r="V81" s="21" t="n"/>
       <c r="W81" s="21" t="n"/>
@@ -5091,7 +5113,9 @@
       <c r="S82" s="21" t="n">
         <v>0.33</v>
       </c>
-      <c r="T82" s="21" t="n"/>
+      <c r="T82" s="21" t="n">
+        <v>0.16</v>
+      </c>
       <c r="U82" s="21" t="n"/>
       <c r="V82" s="21" t="n"/>
       <c r="W82" s="21" t="n"/>
@@ -8456,103 +8480,103 @@
           <t>% AVANCE EJECUTADO SEMANAL</t>
         </is>
       </c>
-      <c r="E148" s="24">
+      <c r="E148" s="27">
         <f>SUMPRODUCT($C$7:$C$146,E7:E146)</f>
         <v/>
       </c>
-      <c r="F148" s="24">
+      <c r="F148" s="27">
         <f>SUMPRODUCT($C$7:$C$146,F7:F146)</f>
         <v/>
       </c>
-      <c r="G148" s="24">
+      <c r="G148" s="27">
         <f>SUMPRODUCT($C$7:$C$146,G7:G146)</f>
         <v/>
       </c>
-      <c r="H148" s="24">
+      <c r="H148" s="27">
         <f>SUMPRODUCT($C$7:$C$146,H7:H146)</f>
         <v/>
       </c>
-      <c r="I148" s="24">
+      <c r="I148" s="27">
         <f>SUMPRODUCT($C$7:$C$146,I7:I146)</f>
         <v/>
       </c>
-      <c r="J148" s="24">
+      <c r="J148" s="27">
         <f>SUMPRODUCT($C$7:$C$146,J7:J146)</f>
         <v/>
       </c>
-      <c r="K148" s="24">
+      <c r="K148" s="27">
         <f>SUMPRODUCT($C$7:$C$146,K7:K146)</f>
         <v/>
       </c>
-      <c r="L148" s="24">
+      <c r="L148" s="27">
         <f>SUMPRODUCT($C$7:$C$146,L7:L146)</f>
         <v/>
       </c>
-      <c r="M148" s="24">
+      <c r="M148" s="27">
         <f>SUMPRODUCT($C$7:$C$146,M7:M146)</f>
         <v/>
       </c>
-      <c r="N148" s="24">
+      <c r="N148" s="27">
         <f>SUMPRODUCT($C$7:$C$146,N7:N146)</f>
         <v/>
       </c>
-      <c r="O148" s="24">
+      <c r="O148" s="27">
         <f>SUMPRODUCT($C$7:$C$146,O7:O146)</f>
         <v/>
       </c>
-      <c r="P148" s="24">
+      <c r="P148" s="27">
         <f>SUMPRODUCT($C$7:$C$146,P7:P146)</f>
         <v/>
       </c>
-      <c r="Q148" s="24">
+      <c r="Q148" s="27">
         <f>SUMPRODUCT($C$7:$C$146,Q7:Q146)</f>
         <v/>
       </c>
-      <c r="R148" s="24">
+      <c r="R148" s="27">
         <f>SUMPRODUCT($C$7:$C$146,R7:R146)</f>
         <v/>
       </c>
-      <c r="S148" s="24">
+      <c r="S148" s="27">
         <f>SUMPRODUCT($C$7:$C$146,S7:S146)</f>
         <v/>
       </c>
-      <c r="T148" s="24">
+      <c r="T148" s="27">
         <f>SUMPRODUCT($C$7:$C$146,T7:T146)</f>
         <v/>
       </c>
-      <c r="U148" s="24">
+      <c r="U148" s="27">
         <f>SUMPRODUCT($C$7:$C$146,U7:U146)</f>
         <v/>
       </c>
-      <c r="V148" s="24">
+      <c r="V148" s="27">
         <f>SUMPRODUCT($C$7:$C$146,V7:V146)</f>
         <v/>
       </c>
-      <c r="W148" s="24">
+      <c r="W148" s="27">
         <f>SUMPRODUCT($C$7:$C$146,W7:W146)</f>
         <v/>
       </c>
-      <c r="X148" s="24">
+      <c r="X148" s="27">
         <f>SUMPRODUCT($C$7:$C$146,X7:X146)</f>
         <v/>
       </c>
-      <c r="Y148" s="24">
+      <c r="Y148" s="27">
         <f>SUMPRODUCT($C$7:$C$146,Y7:Y146)</f>
         <v/>
       </c>
-      <c r="Z148" s="24">
+      <c r="Z148" s="27">
         <f>SUMPRODUCT($C$7:$C$146,Z7:Z146)</f>
         <v/>
       </c>
-      <c r="AA148" s="24">
+      <c r="AA148" s="27">
         <f>SUMPRODUCT($C$7:$C$146,AA7:AA146)</f>
         <v/>
       </c>
-      <c r="AB148" s="24">
+      <c r="AB148" s="27">
         <f>SUMPRODUCT($C$7:$C$146,AB7:AB146)</f>
         <v/>
       </c>
-      <c r="AC148" s="24">
+      <c r="AC148" s="27">
         <f>SUMPRODUCT($C$7:$C$146,AC7:AC146)</f>
         <v/>
       </c>
@@ -8563,107 +8587,107 @@
           <t>% AVANCE EJECUTADO ACUMULADO</t>
         </is>
       </c>
-      <c r="E149" s="24">
+      <c r="E149" s="27">
         <f>E148</f>
         <v/>
       </c>
-      <c r="F149" s="24">
+      <c r="F149" s="27">
         <f>E149+F148</f>
         <v/>
       </c>
-      <c r="G149" s="24">
+      <c r="G149" s="27">
         <f>F149+G148</f>
         <v/>
       </c>
-      <c r="H149" s="24">
+      <c r="H149" s="27">
         <f>G149+H148</f>
         <v/>
       </c>
-      <c r="I149" s="24">
+      <c r="I149" s="27">
         <f>H149+I148</f>
         <v/>
       </c>
-      <c r="J149" s="24">
+      <c r="J149" s="27">
         <f>I149+J148</f>
         <v/>
       </c>
-      <c r="K149" s="24">
+      <c r="K149" s="27">
         <f>J149+K148</f>
         <v/>
       </c>
-      <c r="L149" s="24">
+      <c r="L149" s="27">
         <f>K149+L148</f>
         <v/>
       </c>
-      <c r="M149" s="24">
+      <c r="M149" s="27">
         <f>L149+M148</f>
         <v/>
       </c>
-      <c r="N149" s="24">
+      <c r="N149" s="27">
         <f>M149+N148</f>
         <v/>
       </c>
-      <c r="O149" s="24">
+      <c r="O149" s="27">
         <f>N149+O148</f>
         <v/>
       </c>
-      <c r="P149" s="24">
+      <c r="P149" s="27">
         <f>O149+P148</f>
         <v/>
       </c>
-      <c r="Q149" s="24">
+      <c r="Q149" s="27">
         <f>P149+Q148</f>
         <v/>
       </c>
-      <c r="R149" s="24">
+      <c r="R149" s="27">
         <f>Q149+R148</f>
         <v/>
       </c>
-      <c r="S149" s="24">
+      <c r="S149" s="27">
         <f>R149+S148</f>
         <v/>
       </c>
-      <c r="T149" s="24">
+      <c r="T149" s="27">
         <f>S149+T148</f>
         <v/>
       </c>
-      <c r="U149" s="24">
+      <c r="U149" s="27">
         <f>T149+U148</f>
         <v/>
       </c>
-      <c r="V149" s="24">
+      <c r="V149" s="27">
         <f>U149+V148</f>
         <v/>
       </c>
-      <c r="W149" s="24">
+      <c r="W149" s="27">
         <f>V149+W148</f>
         <v/>
       </c>
-      <c r="X149" s="24">
+      <c r="X149" s="27">
         <f>W149+X148</f>
         <v/>
       </c>
-      <c r="Y149" s="24">
+      <c r="Y149" s="27">
         <f>X149+Y148</f>
         <v/>
       </c>
-      <c r="Z149" s="24">
+      <c r="Z149" s="27">
         <f>Y149+Z148</f>
         <v/>
       </c>
-      <c r="AA149" s="24">
+      <c r="AA149" s="27">
         <f>Z149+AA148</f>
         <v/>
       </c>
-      <c r="AB149" s="24">
+      <c r="AB149" s="27">
         <f>AA149+AB148</f>
         <v/>
       </c>
-      <c r="AC149" s="24">
+      <c r="AC149" s="27">
         <f>AB149+AC148</f>
         <v/>
       </c>
-      <c r="AD149" s="25">
+      <c r="AD149" s="28">
         <f>MAX(E149:AC149)</f>
         <v/>
       </c>
@@ -8674,79 +8698,79 @@
           <t>% AVANCE PROGRAMADO SEMANAL (LÍNEA BASE)</t>
         </is>
       </c>
-      <c r="E150" s="24" t="n">
+      <c r="E150" s="27" t="n">
         <v>0.0024070622934496</v>
       </c>
-      <c r="F150" s="24" t="n">
+      <c r="F150" s="27" t="n">
         <v>0.00288847443244886</v>
       </c>
-      <c r="G150" s="24" t="n">
+      <c r="G150" s="27" t="n">
         <v>0.01287576261809254</v>
       </c>
-      <c r="H150" s="24" t="n">
+      <c r="H150" s="27" t="n">
         <v>0.01434932668865004</v>
       </c>
-      <c r="I150" s="24" t="n">
+      <c r="I150" s="27" t="n">
         <v>0.01615690931039519</v>
       </c>
-      <c r="J150" s="24" t="n">
+      <c r="J150" s="27" t="n">
         <v>0.02740335432174093</v>
       </c>
-      <c r="K150" s="24" t="n">
+      <c r="K150" s="27" t="n">
         <v>0.07151344793125795</v>
       </c>
-      <c r="L150" s="24" t="n">
+      <c r="L150" s="27" t="n">
         <v>0.02694305399784365</v>
       </c>
-      <c r="M150" s="24" t="n">
+      <c r="M150" s="27" t="n">
         <v>0.01604536594187696</v>
       </c>
-      <c r="N150" s="24" t="n">
+      <c r="N150" s="27" t="n">
         <v>0.01719377535602788</v>
       </c>
-      <c r="O150" s="24" t="n">
+      <c r="O150" s="27" t="n">
         <v>0.02993398423002183</v>
       </c>
-      <c r="P150" s="24" t="n">
+      <c r="P150" s="27" t="n">
         <v>0.07819684253361391</v>
       </c>
-      <c r="Q150" s="24" t="n">
+      <c r="Q150" s="27" t="n">
         <v>0.06620130788528446</v>
       </c>
-      <c r="R150" s="24" t="n">
+      <c r="R150" s="27" t="n">
         <v>0.08150104106990419</v>
       </c>
-      <c r="S150" s="24" t="n">
+      <c r="S150" s="27" t="n">
         <v>0.06296400476435951</v>
       </c>
-      <c r="T150" s="24" t="n">
+      <c r="T150" s="27" t="n">
         <v>0.05522807184455759</v>
       </c>
-      <c r="U150" s="24" t="n">
+      <c r="U150" s="27" t="n">
         <v>0.07209540160952506</v>
       </c>
-      <c r="V150" s="24" t="n">
+      <c r="V150" s="27" t="n">
         <v>0.05718566578165239</v>
       </c>
-      <c r="W150" s="24" t="n">
+      <c r="W150" s="27" t="n">
         <v>0.03234258409783331</v>
       </c>
-      <c r="X150" s="24" t="n">
+      <c r="X150" s="27" t="n">
         <v>0.04650424823806285</v>
       </c>
-      <c r="Y150" s="24" t="n">
+      <c r="Y150" s="27" t="n">
         <v>0.1355540490349511</v>
       </c>
-      <c r="Z150" s="24" t="n">
+      <c r="Z150" s="27" t="n">
         <v>0.0685970477344994</v>
       </c>
-      <c r="AA150" s="24" t="n">
+      <c r="AA150" s="27" t="n">
         <v>0.002772516196520008</v>
       </c>
-      <c r="AB150" s="24" t="n">
+      <c r="AB150" s="27" t="n">
         <v>0.00224764447596113</v>
       </c>
-      <c r="AC150" s="24" t="n">
+      <c r="AC150" s="27" t="n">
         <v>0.0008990577903844526</v>
       </c>
     </row>
@@ -8756,79 +8780,79 @@
           <t>% AVANCE PROGRAMADO ACUMULADO (LÍNEA BASE)</t>
         </is>
       </c>
-      <c r="E151" s="24" t="n">
+      <c r="E151" s="27" t="n">
         <v>0.0024070622934496</v>
       </c>
-      <c r="F151" s="24" t="n">
+      <c r="F151" s="27" t="n">
         <v>0.00529553672589846</v>
       </c>
-      <c r="G151" s="24" t="n">
+      <c r="G151" s="27" t="n">
         <v>0.018171299343991</v>
       </c>
-      <c r="H151" s="24" t="n">
+      <c r="H151" s="27" t="n">
         <v>0.03252062603264104</v>
       </c>
-      <c r="I151" s="24" t="n">
+      <c r="I151" s="27" t="n">
         <v>0.04867753534303623</v>
       </c>
-      <c r="J151" s="24" t="n">
+      <c r="J151" s="27" t="n">
         <v>0.07608088966477716</v>
       </c>
-      <c r="K151" s="24" t="n">
+      <c r="K151" s="27" t="n">
         <v>0.1475943375960351</v>
       </c>
-      <c r="L151" s="24" t="n">
+      <c r="L151" s="27" t="n">
         <v>0.1745373915938788</v>
       </c>
-      <c r="M151" s="24" t="n">
+      <c r="M151" s="27" t="n">
         <v>0.1905827575357557</v>
       </c>
-      <c r="N151" s="24" t="n">
+      <c r="N151" s="27" t="n">
         <v>0.2077765328917836</v>
       </c>
-      <c r="O151" s="24" t="n">
+      <c r="O151" s="27" t="n">
         <v>0.2377105171218054</v>
       </c>
-      <c r="P151" s="24" t="n">
+      <c r="P151" s="27" t="n">
         <v>0.3159073596554193</v>
       </c>
-      <c r="Q151" s="24" t="n">
+      <c r="Q151" s="27" t="n">
         <v>0.3821086675407038</v>
       </c>
-      <c r="R151" s="24" t="n">
+      <c r="R151" s="27" t="n">
         <v>0.463609708610608</v>
       </c>
-      <c r="S151" s="24" t="n">
+      <c r="S151" s="27" t="n">
         <v>0.5265737133749675</v>
       </c>
-      <c r="T151" s="24" t="n">
+      <c r="T151" s="27" t="n">
         <v>0.5818017852195251</v>
       </c>
-      <c r="U151" s="24" t="n">
+      <c r="U151" s="27" t="n">
         <v>0.6538971868290502</v>
       </c>
-      <c r="V151" s="24" t="n">
+      <c r="V151" s="27" t="n">
         <v>0.7110828526107026</v>
       </c>
-      <c r="W151" s="24" t="n">
+      <c r="W151" s="27" t="n">
         <v>0.7434254367085359</v>
       </c>
-      <c r="X151" s="24" t="n">
+      <c r="X151" s="27" t="n">
         <v>0.7899296849465988</v>
       </c>
-      <c r="Y151" s="24" t="n">
+      <c r="Y151" s="27" t="n">
         <v>0.9254837339815498</v>
       </c>
-      <c r="Z151" s="24" t="n">
+      <c r="Z151" s="27" t="n">
         <v>0.9940807817160492</v>
       </c>
-      <c r="AA151" s="24" t="n">
+      <c r="AA151" s="27" t="n">
         <v>0.9968532979125692</v>
       </c>
-      <c r="AB151" s="24" t="n">
+      <c r="AB151" s="27" t="n">
         <v>0.9991009423885303</v>
       </c>
-      <c r="AC151" s="24" t="n">
+      <c r="AC151" s="27" t="n">
         <v>1.000000000178915</v>
       </c>
     </row>

--- a/seguimiento/galapa-6v091tb7/cronograma-ejecutado.xlsx
+++ b/seguimiento/galapa-6v091tb7/cronograma-ejecutado.xlsx
@@ -1643,7 +1643,11 @@
       <c r="T19" s="21" t="n">
         <v>0.06</v>
       </c>
-      <c r="U19" s="21" t="n"/>
+      <c r="U19" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="V19" s="21" t="n"/>
       <c r="W19" s="21" t="n"/>
       <c r="X19" s="21" t="n"/>
@@ -1700,8 +1704,16 @@
         </is>
       </c>
       <c r="T20" s="21" t="n"/>
-      <c r="U20" s="21" t="n"/>
-      <c r="V20" s="21" t="n"/>
+      <c r="U20" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V20" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="W20" s="21" t="n"/>
       <c r="X20" s="21" t="n"/>
       <c r="Y20" s="21" t="n"/>
@@ -1999,7 +2011,11 @@
       <c r="T25" s="21" t="n"/>
       <c r="U25" s="21" t="n"/>
       <c r="V25" s="21" t="n"/>
-      <c r="W25" s="21" t="n"/>
+      <c r="W25" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="X25" s="21" t="n"/>
       <c r="Y25" s="21" t="n"/>
       <c r="Z25" s="21" t="n"/>
@@ -2056,9 +2072,21 @@
       </c>
       <c r="S26" s="21" t="n"/>
       <c r="T26" s="21" t="n"/>
-      <c r="U26" s="21" t="n"/>
-      <c r="V26" s="21" t="n"/>
-      <c r="W26" s="21" t="n"/>
+      <c r="U26" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V26" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W26" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="X26" s="21" t="n"/>
       <c r="Y26" s="21" t="n"/>
       <c r="Z26" s="21" t="n"/>
@@ -2113,7 +2141,11 @@
           <t>P</t>
         </is>
       </c>
-      <c r="U27" s="21" t="n"/>
+      <c r="U27" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="V27" s="21" t="n"/>
       <c r="W27" s="21" t="n"/>
       <c r="X27" s="21" t="n"/>
@@ -2178,7 +2210,11 @@
       <c r="T28" s="21" t="n">
         <v>0.28</v>
       </c>
-      <c r="U28" s="21" t="n"/>
+      <c r="U28" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="V28" s="21" t="n"/>
       <c r="W28" s="21" t="n"/>
       <c r="X28" s="21" t="n"/>
@@ -2239,7 +2275,11 @@
           <t>P</t>
         </is>
       </c>
-      <c r="W29" s="21" t="n"/>
+      <c r="W29" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="X29" s="21" t="n"/>
       <c r="Y29" s="21" t="n"/>
       <c r="Z29" s="21" t="n"/>
@@ -2294,8 +2334,16 @@
       <c r="T30" s="21" t="n"/>
       <c r="U30" s="21" t="n"/>
       <c r="V30" s="21" t="n"/>
-      <c r="W30" s="21" t="n"/>
-      <c r="X30" s="21" t="n"/>
+      <c r="W30" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="X30" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Y30" s="21" t="n"/>
       <c r="Z30" s="21" t="n"/>
       <c r="AA30" s="21" t="n"/>
@@ -2347,7 +2395,11 @@
       <c r="V31" s="21" t="n"/>
       <c r="W31" s="21" t="n"/>
       <c r="X31" s="21" t="n"/>
-      <c r="Y31" s="21" t="n"/>
+      <c r="Y31" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Z31" s="21" t="n"/>
       <c r="AA31" s="21" t="n"/>
       <c r="AB31" s="21" t="n"/>
@@ -2495,8 +2547,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="V34" s="21" t="n"/>
-      <c r="W34" s="21" t="n"/>
+      <c r="V34" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W34" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="X34" s="21" t="n"/>
       <c r="Y34" s="21" t="n"/>
       <c r="Z34" s="21" t="n"/>
@@ -2554,8 +2614,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="V35" s="21" t="n"/>
-      <c r="W35" s="21" t="n"/>
+      <c r="V35" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W35" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="X35" s="21" t="n"/>
       <c r="Y35" s="21" t="n"/>
       <c r="Z35" s="21" t="n"/>
@@ -2610,8 +2678,16 @@
       </c>
       <c r="U36" s="21" t="n"/>
       <c r="V36" s="21" t="n"/>
-      <c r="W36" s="21" t="n"/>
-      <c r="X36" s="21" t="n"/>
+      <c r="W36" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="X36" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Y36" s="21" t="n"/>
       <c r="Z36" s="21" t="n"/>
       <c r="AA36" s="21" t="n"/>
@@ -2665,8 +2741,16 @@
       </c>
       <c r="U37" s="21" t="n"/>
       <c r="V37" s="21" t="n"/>
-      <c r="W37" s="21" t="n"/>
-      <c r="X37" s="21" t="n"/>
+      <c r="W37" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="X37" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Y37" s="21" t="n"/>
       <c r="Z37" s="21" t="n"/>
       <c r="AA37" s="21" t="n"/>
@@ -2720,8 +2804,16 @@
       </c>
       <c r="U38" s="21" t="n"/>
       <c r="V38" s="21" t="n"/>
-      <c r="W38" s="21" t="n"/>
-      <c r="X38" s="21" t="n"/>
+      <c r="W38" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="X38" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Y38" s="21" t="n"/>
       <c r="Z38" s="21" t="n"/>
       <c r="AA38" s="21" t="n"/>
@@ -2771,7 +2863,11 @@
       <c r="T39" s="21" t="n"/>
       <c r="U39" s="21" t="n"/>
       <c r="V39" s="21" t="n"/>
-      <c r="W39" s="21" t="n"/>
+      <c r="W39" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="X39" s="21" t="n"/>
       <c r="Y39" s="21" t="n"/>
       <c r="Z39" s="21" t="n"/>
@@ -2822,7 +2918,11 @@
       <c r="T40" s="21" t="n"/>
       <c r="U40" s="21" t="n"/>
       <c r="V40" s="21" t="n"/>
-      <c r="W40" s="21" t="n"/>
+      <c r="W40" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="X40" s="21" t="n"/>
       <c r="Y40" s="21" t="n"/>
       <c r="Z40" s="21" t="n"/>
@@ -3429,9 +3529,21 @@
       </c>
       <c r="S51" s="21" t="n"/>
       <c r="T51" s="21" t="n"/>
-      <c r="U51" s="21" t="n"/>
-      <c r="V51" s="21" t="n"/>
-      <c r="W51" s="21" t="n"/>
+      <c r="U51" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V51" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W51" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="X51" s="21" t="n"/>
       <c r="Y51" s="21" t="n"/>
       <c r="Z51" s="21" t="n"/>
@@ -3489,9 +3601,21 @@
         </is>
       </c>
       <c r="U52" s="21" t="n"/>
-      <c r="V52" s="21" t="n"/>
-      <c r="W52" s="21" t="n"/>
-      <c r="X52" s="21" t="n"/>
+      <c r="V52" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W52" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="X52" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Y52" s="21" t="n"/>
       <c r="Z52" s="21" t="n"/>
       <c r="AA52" s="21" t="n"/>
@@ -3548,9 +3672,21 @@
         </is>
       </c>
       <c r="U53" s="21" t="n"/>
-      <c r="V53" s="21" t="n"/>
-      <c r="W53" s="21" t="n"/>
-      <c r="X53" s="21" t="n"/>
+      <c r="V53" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W53" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="X53" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Y53" s="21" t="n"/>
       <c r="Z53" s="21" t="n"/>
       <c r="AA53" s="21" t="n"/>
@@ -3618,7 +3754,11 @@
           <t>P</t>
         </is>
       </c>
-      <c r="Y54" s="21" t="n"/>
+      <c r="Y54" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Z54" s="21" t="n"/>
       <c r="AA54" s="21" t="n"/>
       <c r="AB54" s="21" t="n"/>
@@ -4817,8 +4957,16 @@
       <c r="T77" s="21" t="n">
         <v>0.2</v>
       </c>
-      <c r="U77" s="21" t="n"/>
-      <c r="V77" s="21" t="n"/>
+      <c r="U77" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V77" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="W77" s="21" t="n"/>
       <c r="X77" s="21" t="n"/>
       <c r="Y77" s="21" t="n"/>
@@ -4937,7 +5085,11 @@
       <c r="T79" s="21" t="n">
         <v>0.32</v>
       </c>
-      <c r="U79" s="21" t="n"/>
+      <c r="U79" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="V79" s="21" t="n"/>
       <c r="W79" s="21" t="n"/>
       <c r="X79" s="21" t="n"/>
@@ -4996,7 +5148,11 @@
       <c r="T80" s="21" t="n">
         <v>0.32</v>
       </c>
-      <c r="U80" s="21" t="n"/>
+      <c r="U80" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="V80" s="21" t="n"/>
       <c r="W80" s="21" t="n"/>
       <c r="X80" s="21" t="n"/>
@@ -5055,7 +5211,11 @@
       <c r="T81" s="21" t="n">
         <v>0.06</v>
       </c>
-      <c r="U81" s="21" t="n"/>
+      <c r="U81" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="V81" s="21" t="n"/>
       <c r="W81" s="21" t="n"/>
       <c r="X81" s="21" t="n"/>
@@ -5116,7 +5276,11 @@
       <c r="T82" s="21" t="n">
         <v>0.16</v>
       </c>
-      <c r="U82" s="21" t="n"/>
+      <c r="U82" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="V82" s="21" t="n"/>
       <c r="W82" s="21" t="n"/>
       <c r="X82" s="21" t="n"/>
@@ -5167,7 +5331,11 @@
       <c r="R83" s="21" t="n"/>
       <c r="S83" s="21" t="n"/>
       <c r="T83" s="21" t="n"/>
-      <c r="U83" s="21" t="n"/>
+      <c r="U83" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="V83" s="21" t="n"/>
       <c r="W83" s="21" t="n"/>
       <c r="X83" s="21" t="n"/>
@@ -5218,7 +5386,11 @@
       <c r="R84" s="21" t="n"/>
       <c r="S84" s="21" t="n"/>
       <c r="T84" s="21" t="n"/>
-      <c r="U84" s="21" t="n"/>
+      <c r="U84" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="V84" s="21" t="n"/>
       <c r="W84" s="21" t="n"/>
       <c r="X84" s="21" t="n"/>
@@ -5273,8 +5445,16 @@
       <c r="R85" s="21" t="n"/>
       <c r="S85" s="21" t="n"/>
       <c r="T85" s="21" t="n"/>
-      <c r="U85" s="21" t="n"/>
-      <c r="V85" s="21" t="n"/>
+      <c r="U85" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V85" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="W85" s="21" t="n"/>
       <c r="X85" s="21" t="n"/>
       <c r="Y85" s="21" t="n"/>
@@ -5328,8 +5508,16 @@
       <c r="R86" s="21" t="n"/>
       <c r="S86" s="21" t="n"/>
       <c r="T86" s="21" t="n"/>
-      <c r="U86" s="21" t="n"/>
-      <c r="V86" s="21" t="n"/>
+      <c r="U86" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V86" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="W86" s="21" t="n"/>
       <c r="X86" s="21" t="n"/>
       <c r="Y86" s="21" t="n"/>
@@ -5379,7 +5567,11 @@
       <c r="R87" s="21" t="n"/>
       <c r="S87" s="21" t="n"/>
       <c r="T87" s="21" t="n"/>
-      <c r="U87" s="21" t="n"/>
+      <c r="U87" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="V87" s="21" t="n"/>
       <c r="W87" s="21" t="n"/>
       <c r="X87" s="21" t="n"/>
@@ -5477,8 +5669,16 @@
       <c r="R89" s="21" t="n"/>
       <c r="S89" s="21" t="n"/>
       <c r="T89" s="21" t="n"/>
-      <c r="U89" s="21" t="n"/>
-      <c r="V89" s="21" t="n"/>
+      <c r="U89" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V89" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="W89" s="21" t="n"/>
       <c r="X89" s="21" t="n"/>
       <c r="Y89" s="21" t="n"/>
@@ -5532,8 +5732,16 @@
       <c r="R90" s="21" t="n"/>
       <c r="S90" s="21" t="n"/>
       <c r="T90" s="21" t="n"/>
-      <c r="U90" s="21" t="n"/>
-      <c r="V90" s="21" t="n"/>
+      <c r="U90" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V90" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="W90" s="21" t="n"/>
       <c r="X90" s="21" t="n"/>
       <c r="Y90" s="21" t="n"/>
@@ -5583,7 +5791,11 @@
       <c r="R91" s="21" t="n"/>
       <c r="S91" s="21" t="n"/>
       <c r="T91" s="21" t="n"/>
-      <c r="U91" s="21" t="n"/>
+      <c r="U91" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="V91" s="21" t="n"/>
       <c r="W91" s="21" t="n"/>
       <c r="X91" s="21" t="n"/>
@@ -5638,8 +5850,16 @@
       <c r="R92" s="21" t="n"/>
       <c r="S92" s="21" t="n"/>
       <c r="T92" s="21" t="n"/>
-      <c r="U92" s="21" t="n"/>
-      <c r="V92" s="21" t="n"/>
+      <c r="U92" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V92" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="W92" s="21" t="n"/>
       <c r="X92" s="21" t="n"/>
       <c r="Y92" s="21" t="n"/>
@@ -5693,8 +5913,16 @@
       <c r="R93" s="21" t="n"/>
       <c r="S93" s="21" t="n"/>
       <c r="T93" s="21" t="n"/>
-      <c r="U93" s="21" t="n"/>
-      <c r="V93" s="21" t="n"/>
+      <c r="U93" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V93" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="W93" s="21" t="n"/>
       <c r="X93" s="21" t="n"/>
       <c r="Y93" s="21" t="n"/>
@@ -7856,7 +8084,11 @@
       <c r="V134" s="21" t="n"/>
       <c r="W134" s="21" t="n"/>
       <c r="X134" s="21" t="n"/>
-      <c r="Y134" s="21" t="n"/>
+      <c r="Y134" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Z134" s="21" t="n"/>
       <c r="AA134" s="21" t="n"/>
       <c r="AB134" s="21" t="n"/>
@@ -7907,7 +8139,11 @@
       <c r="V135" s="21" t="n"/>
       <c r="W135" s="21" t="n"/>
       <c r="X135" s="21" t="n"/>
-      <c r="Y135" s="21" t="n"/>
+      <c r="Y135" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Z135" s="21" t="n"/>
       <c r="AA135" s="21" t="n"/>
       <c r="AB135" s="21" t="n"/>
@@ -7958,7 +8194,11 @@
       <c r="V136" s="21" t="n"/>
       <c r="W136" s="21" t="n"/>
       <c r="X136" s="21" t="n"/>
-      <c r="Y136" s="21" t="n"/>
+      <c r="Y136" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Z136" s="21" t="n"/>
       <c r="AA136" s="21" t="n"/>
       <c r="AB136" s="21" t="n"/>
@@ -8009,7 +8249,11 @@
       <c r="V137" s="21" t="n"/>
       <c r="W137" s="21" t="n"/>
       <c r="X137" s="21" t="n"/>
-      <c r="Y137" s="21" t="n"/>
+      <c r="Y137" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Z137" s="21" t="n"/>
       <c r="AA137" s="21" t="n"/>
       <c r="AB137" s="21" t="n"/>
@@ -8060,7 +8304,11 @@
       <c r="V138" s="21" t="n"/>
       <c r="W138" s="21" t="n"/>
       <c r="X138" s="21" t="n"/>
-      <c r="Y138" s="21" t="n"/>
+      <c r="Y138" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Z138" s="21" t="n"/>
       <c r="AA138" s="21" t="n"/>
       <c r="AB138" s="21" t="n"/>
@@ -8111,7 +8359,11 @@
       <c r="V139" s="21" t="n"/>
       <c r="W139" s="21" t="n"/>
       <c r="X139" s="21" t="n"/>
-      <c r="Y139" s="21" t="n"/>
+      <c r="Y139" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Z139" s="21" t="n"/>
       <c r="AA139" s="21" t="n"/>
       <c r="AB139" s="21" t="n"/>
@@ -8204,7 +8456,11 @@
       <c r="U141" s="21" t="n"/>
       <c r="V141" s="21" t="n"/>
       <c r="W141" s="21" t="n"/>
-      <c r="X141" s="21" t="n"/>
+      <c r="X141" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Y141" s="21" t="n"/>
       <c r="Z141" s="21" t="n"/>
       <c r="AA141" s="21" t="n"/>
@@ -8260,8 +8516,16 @@
       <c r="V142" s="21" t="n"/>
       <c r="W142" s="21" t="n"/>
       <c r="X142" s="21" t="n"/>
-      <c r="Y142" s="21" t="n"/>
-      <c r="Z142" s="21" t="n"/>
+      <c r="Y142" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Z142" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="AA142" s="21" t="n"/>
       <c r="AB142" s="21" t="n"/>
       <c r="AC142" s="21" t="n"/>
@@ -8312,7 +8576,11 @@
       <c r="W143" s="21" t="n"/>
       <c r="X143" s="21" t="n"/>
       <c r="Y143" s="21" t="n"/>
-      <c r="Z143" s="21" t="n"/>
+      <c r="Z143" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="AA143" s="21" t="n"/>
       <c r="AB143" s="21" t="n"/>
       <c r="AC143" s="21" t="n"/>
@@ -8363,7 +8631,11 @@
       <c r="W144" s="21" t="n"/>
       <c r="X144" s="21" t="n"/>
       <c r="Y144" s="21" t="n"/>
-      <c r="Z144" s="21" t="n"/>
+      <c r="Z144" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="AA144" s="21" t="n"/>
       <c r="AB144" s="21" t="n"/>
       <c r="AC144" s="21" t="n"/>
